--- a/data/MEL_Indicator_Reference.xlsx
+++ b/data/MEL_Indicator_Reference.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species_by_Sector" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_by_Sector" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring_Approaches" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Monitoring_Approaches'!$A$1:$F$57</definedName>
@@ -181,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -261,6 +262,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3619,7 +3626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5182,6 +5189,136 @@
       </c>
       <c r="F57" s="29" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Farm records</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>harvest;yield;biomass harvested</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Farm record. Feeds N &amp; P bioextraction, shell carbon and product-replacement indicators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Farm records</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Stock numbers by size class</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>standing stock;size class;standing biomass</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Farm record. Feeds the water filtration rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Farm records</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Harvest and shell end uses</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>end use;shell recycling;disposal;product</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Farm record. Where the crop or shells go after harvest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Farm records</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Fuel and energy use</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>fuel;energy;diesel;electricity;life cycle;lca</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Farm record. Feeds the cradle-to-grave (LCA) indicators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Farm records</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Sea-lice and disease checks on stock</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>sea lice;lice count;parasite;pathogen;disease</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Farm record (finfish). Proposed Oct 2026 for the net-pen indicator; confirm.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5194,7 +5331,4093 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:AF34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="46" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="31" max="31"/>
+    <col width="36" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>Indicator Code</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>Indicator Name</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Picture</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Plain-language summary</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>Picture caption</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>Part 1 label</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>Part 1 methods</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>Part 1 hint</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>Part 2 label</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>Part 2 methods</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>Part 2 hint</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>Part 3 label</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>Part 3 methods</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>Part 3 hint</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>Context methods</t>
+        </is>
+      </c>
+      <c r="R1" s="30" t="inlineStr">
+        <is>
+          <t>Q1 text</t>
+        </is>
+      </c>
+      <c r="S1" s="30" t="inlineStr">
+        <is>
+          <t>Q1 options</t>
+        </is>
+      </c>
+      <c r="T1" s="30" t="inlineStr">
+        <is>
+          <t>Q1 weight</t>
+        </is>
+      </c>
+      <c r="U1" s="30" t="inlineStr">
+        <is>
+          <t>Q1 gap</t>
+        </is>
+      </c>
+      <c r="V1" s="30" t="inlineStr">
+        <is>
+          <t>Q2 text</t>
+        </is>
+      </c>
+      <c r="W1" s="30" t="inlineStr">
+        <is>
+          <t>Q2 options</t>
+        </is>
+      </c>
+      <c r="X1" s="30" t="inlineStr">
+        <is>
+          <t>Q2 weight</t>
+        </is>
+      </c>
+      <c r="Y1" s="30" t="inlineStr">
+        <is>
+          <t>Q2 gap</t>
+        </is>
+      </c>
+      <c r="Z1" s="30" t="inlineStr">
+        <is>
+          <t>Q3 text</t>
+        </is>
+      </c>
+      <c r="AA1" s="30" t="inlineStr">
+        <is>
+          <t>Q3 options</t>
+        </is>
+      </c>
+      <c r="AB1" s="30" t="inlineStr">
+        <is>
+          <t>Q3 weight</t>
+        </is>
+      </c>
+      <c r="AC1" s="30" t="inlineStr">
+        <is>
+          <t>Q3 gap</t>
+        </is>
+      </c>
+      <c r="AD1" s="30" t="inlineStr">
+        <is>
+          <t>First step</t>
+        </is>
+      </c>
+      <c r="AE1" s="30" t="inlineStr">
+        <is>
+          <t>First step (short)</t>
+        </is>
+      </c>
+      <c r="AF1" s="30" t="inlineStr">
+        <is>
+          <t>Note when in place</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-1.1.1</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>Life growing on your lines and seaweed</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>The small animals that live on your seaweed and lines, such as tiny shrimp-like animals, snails and sea mats. Plenty of native species, and many different kinds, suggest your farm is giving local life a place to live.</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>Close-up of native animals living on a kelp blade</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>Checks of lines or seaweed</t>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota on lines / structures; Epifauna on crop / rope; Invertebrate collectors / fauna traps; Settlement plates / artificial substrata</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="n"/>
+      <c r="K2" s="31" t="n"/>
+      <c r="L2" s="31" t="n"/>
+      <c r="M2" s="31" t="n"/>
+      <c r="N2" s="31" t="n"/>
+      <c r="O2" s="31" t="n"/>
+      <c r="P2" s="31" t="n"/>
+      <c r="Q2" s="31" t="n"/>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>Where do you check?</t>
+        </is>
+      </c>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>Inside the farm only=0.5; Inside and at the edge of the farm=1</t>
+        </is>
+      </c>
+      <c r="T2" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" s="31" t="inlineStr">
+        <is>
+          <t>Add checks at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V2" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W2" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X2" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y2" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="Z2" s="31" t="inlineStr">
+        <is>
+          <t>What do you note down?</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr">
+        <is>
+          <t>Counts and names (species or groups)=1; What’s there, without counts=0.5; Only whether there’s fouling=0</t>
+        </is>
+      </c>
+      <c r="AB2" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="31" t="inlineStr">
+        <is>
+          <t>Count what you find and name it to species or group; that gives the abundance and diversity the Framework asks for.</t>
+        </is>
+      </c>
+      <c r="AD2" s="31" t="inlineStr">
+        <is>
+          <t>Strip a few blades or a section of line each season and count what’s living on them.</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Strip a few blades or a section of line each season and count what’s living on them.</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Mobile fauna</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-1.2.1</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>Fish, crabs and other visitors</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>Fish, crabs and other animals that move around and use your farm. Counting what visits, and how many kinds, shows whether the farm works as habitat, without adding extra fishing pressure.</t>
+        </is>
+      </c>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line records the fish and other animals that visit</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>Video or visual counts</t>
+        </is>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects; Nets &amp; baited traps; Towed video / ROV</t>
+        </is>
+      </c>
+      <c r="J3" s="31" t="n"/>
+      <c r="K3" s="31" t="n"/>
+      <c r="L3" s="31" t="n"/>
+      <c r="M3" s="31" t="n"/>
+      <c r="N3" s="31" t="n"/>
+      <c r="O3" s="31" t="n"/>
+      <c r="P3" s="31" t="n"/>
+      <c r="Q3" s="31" t="n"/>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>Where do you check?</t>
+        </is>
+      </c>
+      <c r="S3" s="31" t="inlineStr">
+        <is>
+          <t>Inside the farm only=0.5; Inside and at the edge of the farm=1</t>
+        </is>
+      </c>
+      <c r="T3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" s="31" t="inlineStr">
+        <is>
+          <t>Add checks at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V3" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W3" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X3" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="Z3" s="31" t="inlineStr">
+        <is>
+          <t>What do you note down?</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr">
+        <is>
+          <t>Counts and names (species or groups)=1; What’s there, without counts=0.5; Not much detail=0</t>
+        </is>
+      </c>
+      <c r="AB3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="31" t="inlineStr">
+        <is>
+          <t>Count what you find and name it to species or group.</t>
+        </is>
+      </c>
+      <c r="AD3" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line (a GoPro works), set once a season inside the farm and at its edge.</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line (a GoPro works), set once a season inside the farm and at its edge.</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.3.1</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-1.3.1</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>Animals living in the seabed under your farm</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>Worms, clams and other small animals that live buried in the seabed under and around your farm. A healthy mix of them shows the seabed is in good shape. They’re collected with a grab or core and sorted later.</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>A grab sample from the seabed under the farm</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>Seabed animal samples</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna community</t>
+        </is>
+      </c>
+      <c r="J4" s="31" t="n"/>
+      <c r="K4" s="31" t="n"/>
+      <c r="L4" s="31" t="n"/>
+      <c r="M4" s="31" t="n"/>
+      <c r="N4" s="31" t="n"/>
+      <c r="O4" s="31" t="n"/>
+      <c r="P4" s="31" t="n"/>
+      <c r="Q4" s="31" t="n"/>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take seabed samples?</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>Under the farm only=0.5; Under the farm and at its edge=1</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="31" t="inlineStr">
+        <is>
+          <t>Add seabed samples at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>Sample once a season.</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>Who sorts and identifies the animals?</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>A lab or trained partner=1; We sort them ourselves=0.6</t>
+        </is>
+      </c>
+      <c r="AB4" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>Send samples to a lab or trained partner to sort and identify.</t>
+        </is>
+      </c>
+      <c r="AD4" s="31" t="inlineStr">
+        <is>
+          <t>Seabed grabs or cores under the farm and at its edge each season, with a lab to sort them.</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Seabed grabs or cores under the farm and at its edge each season, with a lab to sort them.</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.4.1</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Sediment characteristics</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-1.4.1</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>The health of the seabed under your farm</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>What the seabed under your farm is like: how much organic matter it holds, and whether it has enough oxygen or smells of rotten eggs (sulfide). Comparing it with nearby seabed shows whether farming keeps it as healthy as the surroundings.</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Seabed photos under the farm and at a nearby spot</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>Seabed condition</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Sediment chemistry (OC / TN / redox / AVS); Sediment-profile imaging (SPI); MOM-B condition survey; Grain size / particle size</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="n"/>
+      <c r="K5" s="31" t="n"/>
+      <c r="L5" s="31" t="n"/>
+      <c r="M5" s="31" t="n"/>
+      <c r="N5" s="31" t="n"/>
+      <c r="O5" s="31" t="n"/>
+      <c r="P5" s="31" t="n"/>
+      <c r="Q5" s="31" t="n"/>
+      <c r="R5" s="31" t="inlineStr">
+        <is>
+          <t>Where do you sample the seabed?</t>
+        </is>
+      </c>
+      <c r="S5" s="31" t="inlineStr">
+        <is>
+          <t>Under the farm only=0.5; Under the farm and at a similar spot nearby=1</t>
+        </is>
+      </c>
+      <c r="T5" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="31" t="inlineStr">
+        <is>
+          <t>Add a seabed sample at a similar spot nearby, away from the farm.</t>
+        </is>
+      </c>
+      <c r="V5" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W5" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Twice a year or more=1</t>
+        </is>
+      </c>
+      <c r="X5" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y5" s="31" t="inlineStr">
+        <is>
+          <t>Sample at least twice a year.</t>
+        </is>
+      </c>
+      <c r="Z5" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA5" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD5" s="31" t="inlineStr">
+        <is>
+          <t>Seabed photos under the farm and at a nearby spot, twice a year.</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Seabed photos under the farm and at a nearby spot, twice a year.</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.1.1</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Associated community composition</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-2.1.1</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>All the life at your farm, compared with nearby</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>The whole community of life at your farm: on the seaweed and lines, swimming around them and living in the seabed below. Comparing it with similar natural habitat nearby, like wild seaweed or seagrass, shows whether your farm adds to local biodiversity.</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>Life on the lines, in the water and in the seabed, compared with wild seaweed nearby</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>Life on the lines and seaweed</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota on lines / structures; Epifauna on crop / rope; Invertebrate collectors / fauna traps; Settlement plates / artificial substrata</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="n"/>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>Fish and other mobile animals</t>
+        </is>
+      </c>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects; Nets &amp; baited traps; Towed video / ROV</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>a camera on a line works</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>Seabed animals (infauna)</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna community</t>
+        </is>
+      </c>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>sediment grabs or cores</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="n"/>
+      <c r="R6" s="31" t="inlineStr">
+        <is>
+          <t>Do you also survey similar habitat outside the farm?</t>
+        </is>
+      </c>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>No, inside only=0.5; Yes=1</t>
+        </is>
+      </c>
+      <c r="T6" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" s="31" t="inlineStr">
+        <is>
+          <t>Add a similar habitat outside the farm to compare against.</t>
+        </is>
+      </c>
+      <c r="V6" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W6" s="31" t="inlineStr">
+        <is>
+          <t>Less than once a year=0.4; Every year=1</t>
+        </is>
+      </c>
+      <c r="X6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="31" t="inlineStr">
+        <is>
+          <t>Repeat it every year.</t>
+        </is>
+      </c>
+      <c r="Z6" s="31" t="n"/>
+      <c r="AA6" s="31" t="n"/>
+      <c r="AB6" s="31" t="n"/>
+      <c r="AC6" s="31" t="n"/>
+      <c r="AD6" s="31" t="inlineStr">
+        <is>
+          <t>Start with one part, such as counts of life on your lines, and add the others over time.</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Start with one part, such as counts of life on your lines, and add the others over time.</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.2.1</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Spawning / recruitment</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_HB-2.2.1</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>Young fish growing up at your farm</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Signs that fish and other animals breed at your farm, or that their young settle and grow there. A stereo camera can tell young fish from adults by their size. It shows whether your farm works as a nursery.</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>A stereo camera measures fish sizes, picking out the young ones</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>Video of young fish</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV)</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="n"/>
+      <c r="K7" s="31" t="n"/>
+      <c r="L7" s="31" t="n"/>
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="31" t="n"/>
+      <c r="O7" s="31" t="n"/>
+      <c r="P7" s="31" t="n"/>
+      <c r="Q7" s="31" t="n"/>
+      <c r="R7" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="T7" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U7" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="V7" s="31" t="inlineStr">
+        <is>
+          <t>Do you measure fish sizes from the video?</t>
+        </is>
+      </c>
+      <c r="W7" s="31" t="inlineStr">
+        <is>
+          <t>Yes, with a stereo camera or scale bar=1; Rough sizes only=0.5; No=0</t>
+        </is>
+      </c>
+      <c r="X7" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="31" t="inlineStr">
+        <is>
+          <t>Add a scale bar or a stereo camera so young fish can be measured.</t>
+        </is>
+      </c>
+      <c r="Z7" s="31" t="n"/>
+      <c r="AA7" s="31" t="n"/>
+      <c r="AB7" s="31" t="n"/>
+      <c r="AC7" s="31" t="n"/>
+      <c r="AD7" s="31" t="inlineStr">
+        <is>
+          <t>A stereo camera (two cameras side by side) in the farm each season, so young fish can be measured.</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>A stereo camera (two cameras side by side) in the farm each season, so young fish can be measured.</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.1.1</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>N &amp; P bioextraction</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_WQ-1.1.1</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Nutrients your harvest takes out of the water</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>The nitrogen and phosphorus your seaweed takes up as it grows. At harvest those nutrients leave the water with the crop, so less is left to feed algal blooms. It’s worked out from your harvest weights and published values for your species.</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>Nutrients built into your seaweed leave the water at harvest</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="n"/>
+      <c r="K8" s="31" t="n"/>
+      <c r="L8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="31" t="n"/>
+      <c r="O8" s="31" t="n"/>
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>Tissue elemental (CHN) analysis</t>
+        </is>
+      </c>
+      <c r="R8" s="31" t="inlineStr">
+        <is>
+          <t>Do you weigh every harvest?</t>
+        </is>
+      </c>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>Every harvest=1; Some harvests=0.5</t>
+        </is>
+      </c>
+      <c r="T8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" s="31" t="inlineStr">
+        <is>
+          <t>Weigh every harvest, or count it and convert to weight.</t>
+        </is>
+      </c>
+      <c r="V8" s="31" t="inlineStr">
+        <is>
+          <t>Where do your harvest weights end up?</t>
+        </is>
+      </c>
+      <c r="W8" s="31" t="inlineStr">
+        <is>
+          <t>One logbook or spreadsheet=1; Spread across receipts or memory=0.3</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="31" t="inlineStr">
+        <is>
+          <t>Keep the year’s harvest weights together in one log.</t>
+        </is>
+      </c>
+      <c r="Z8" s="31" t="n"/>
+      <c r="AA8" s="31" t="n"/>
+      <c r="AB8" s="31" t="n"/>
+      <c r="AC8" s="31" t="n"/>
+      <c r="AD8" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest. That, plus published N and P values for your species, is all this indicator needs.</t>
+        </is>
+      </c>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest; with published N and P values for your species, that’s all this needs.</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.2.1</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_WQ-1.2.1</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen in the water around your farm</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>How much oxygen is dissolved in the water. Too many nutrients can push oxygen down, which stresses fish and other sea life. Comparing readings inside and outside the farm shows whether your farm is helping ease that pressure.</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen readings inside the farm and at a spot outside it</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen readings</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="n"/>
+      <c r="K9" s="31" t="n"/>
+      <c r="L9" s="31" t="n"/>
+      <c r="M9" s="31" t="n"/>
+      <c r="N9" s="31" t="n"/>
+      <c r="O9" s="31" t="n"/>
+      <c r="P9" s="31" t="n"/>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>Temperature / salinity; Continuous moored sensors</t>
+        </is>
+      </c>
+      <c r="R9" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take oxygen readings?</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V9" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W9" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X9" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z9" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA9" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD9" s="31" t="inlineStr">
+        <is>
+          <t>A handheld oxygen meter, read at the same time of day inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>A handheld oxygen meter, read at the same time of day inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>WQ 2.1.1</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_WQ-2.1.1</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Tiny algae floating in the water</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>How much microscopic algae (phytoplankton) is floating in the water. Lots of it is a common sign of too many nutrients. Comparing inside and outside the farm shows whether your farm helps keep algae in check, without harming wild populations or other farms.</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Water samples inside and outside the farm show how much algae is in it</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll readings</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a (water)</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="n"/>
+      <c r="K10" s="31" t="n"/>
+      <c r="L10" s="31" t="n"/>
+      <c r="M10" s="31" t="n"/>
+      <c r="N10" s="31" t="n"/>
+      <c r="O10" s="31" t="n"/>
+      <c r="P10" s="31" t="n"/>
+      <c r="Q10" s="31" t="inlineStr">
+        <is>
+          <t>Water clarity / turbidity (Secchi); Temperature / salinity; Satellite ocean colour (chl-a)</t>
+        </is>
+      </c>
+      <c r="R10" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take water samples?</t>
+        </is>
+      </c>
+      <c r="S10" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T10" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V10" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W10" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X10" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z10" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA10" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD10" s="31" t="inlineStr">
+        <is>
+          <t>Water samples sent to a lab, or a chlorophyll sensor, inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Water samples sent to a lab, or a chlorophyll sensor, inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>WQ 2.1.2</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Microorganism &amp; plankton community</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_WQ-2.1.2</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>The tiny life drifting in the water</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>Which microscopic plants, animals and microbes drift in the water, and how many. Sampling inside and outside the farm shows whether these communities stay healthy and productive around your farm. Samples go to a lab for microscopy or DNA.</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>A plankton net and water samples inside and outside the farm</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>Plankton samples</t>
+        </is>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>Phytoplankton community (microscopy); Zooplankton net haul; Flow cytometry; Water eDNA; Size-fractionated pigments (HPLC)</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="n"/>
+      <c r="P11" s="31" t="n"/>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a (water)</t>
+        </is>
+      </c>
+      <c r="R11" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take plankton samples?</t>
+        </is>
+      </c>
+      <c r="S11" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V11" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W11" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X11" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z11" s="31" t="inlineStr">
+        <is>
+          <t>Who identifies what’s in the samples?</t>
+        </is>
+      </c>
+      <c r="AA11" s="31" t="inlineStr">
+        <is>
+          <t>A lab or trained partner=1; We look ourselves=0.5</t>
+        </is>
+      </c>
+      <c r="AB11" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="31" t="inlineStr">
+        <is>
+          <t>Send samples to a lab or trained partner for identification.</t>
+        </is>
+      </c>
+      <c r="AD11" s="31" t="inlineStr">
+        <is>
+          <t>Plankton net tows and water samples inside and outside the farm each season, identified by a lab.</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Plankton net tows and water samples inside and outside the farm each season, identified by a lab.</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>CC 1.1.1</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Biomass replacement of emissions-intensive products</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_CC-1.1.1</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed products that replace higher-carbon ones</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>How much of your seaweed ends up replacing products with a bigger carbon footprint, such as some fertilisers, feeds or packaging. It’s worked out from your harvest, the carbon content of your species and where the crop goes.</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>Your harvest heading into products that replace higher-carbon ones</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>Where your harvest goes</t>
+        </is>
+      </c>
+      <c r="L12" s="31" t="inlineStr">
+        <is>
+          <t>Harvest and shell end uses</t>
+        </is>
+      </c>
+      <c r="M12" s="31" t="inlineStr">
+        <is>
+          <t>buyer or end-use records</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="n"/>
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="31" t="n"/>
+      <c r="Q12" s="31" t="n"/>
+      <c r="R12" s="31" t="inlineStr">
+        <is>
+          <t>How often do you add up what you harvest and where it goes?</t>
+        </is>
+      </c>
+      <c r="S12" s="31" t="inlineStr">
+        <is>
+          <t>Every year=1; Less often=0.4</t>
+        </is>
+      </c>
+      <c r="T12" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" s="31" t="inlineStr">
+        <is>
+          <t>Add it up every year.</t>
+        </is>
+      </c>
+      <c r="V12" s="31" t="inlineStr">
+        <is>
+          <t>Do you weigh every harvest?</t>
+        </is>
+      </c>
+      <c r="W12" s="31" t="inlineStr">
+        <is>
+          <t>Every harvest=1; Some harvests=0.5</t>
+        </is>
+      </c>
+      <c r="X12" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="31" t="inlineStr">
+        <is>
+          <t>Weigh every harvest, or count it and convert to weight.</t>
+        </is>
+      </c>
+      <c r="Z12" s="31" t="n"/>
+      <c r="AA12" s="31" t="n"/>
+      <c r="AB12" s="31" t="n"/>
+      <c r="AC12" s="31" t="n"/>
+      <c r="AD12" s="31" t="inlineStr">
+        <is>
+          <t>Keep harvest weights and a note of what each batch is used for.</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Keep harvest weights and a note of what each batch is used for.</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>CC 1.2.1</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Cradle-to-grave GHG emissions</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_CC-1.2.1</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>Where your seaweed’s carbon ends up</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Where the carbon in your seaweed goes. Bits of frond break off and dissolved carbon leaks out as it grows, then drift away on the currents. Tracking this with water chemistry and current models helps explain how carbon cycles around your farm; it isn’t a claim that the carbon is stored.</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>Fronds and dissolved carbon drifting away from the farm on the current</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>Carbon chemistry in the water</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>Carbonate system (pH / OA); Dissolved / total organic carbon</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>Currents or drift modelling</t>
+        </is>
+      </c>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>Hydrodynamic + particle tracking; ADCP (currents / waves); Coupled biogeochemical / DEB model</t>
+        </is>
+      </c>
+      <c r="M13" s="31" t="inlineStr">
+        <is>
+          <t>usually with a research partner</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="31" t="inlineStr">
+        <is>
+          <t>How often do you sample?</t>
+        </is>
+      </c>
+      <c r="S13" s="31" t="inlineStr">
+        <is>
+          <t>Now and then=0.4; Regularly, or with sensors=1</t>
+        </is>
+      </c>
+      <c r="T13" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" s="31" t="inlineStr">
+        <is>
+          <t>Sample regularly, or add a logging sensor.</t>
+        </is>
+      </c>
+      <c r="V13" s="31" t="inlineStr">
+        <is>
+          <t>Where do you sample?</t>
+        </is>
+      </c>
+      <c r="W13" s="31" t="inlineStr">
+        <is>
+          <t>Inside the farm only=0.5; Inside the farm and in the wider bay=1</t>
+        </is>
+      </c>
+      <c r="X13" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="31" t="inlineStr">
+        <is>
+          <t>Add sampling points in the wider bay, downstream of the farm.</t>
+        </is>
+      </c>
+      <c r="Z13" s="31" t="n"/>
+      <c r="AA13" s="31" t="n"/>
+      <c r="AB13" s="31" t="n"/>
+      <c r="AC13" s="31" t="n"/>
+      <c r="AD13" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: water chemistry sampling plus a current model to follow where the carbon goes.</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: water chemistry sampling plus a current model to follow where the carbon goes.</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>CC 2.1.1</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>pH at farm site</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>seaweed_CC-2.1.1</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>How acidic the water is at your farm</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>pH shows how acidic the water is. Growing seaweed takes up carbon dioxide, which can raise pH around the farm where ocean acidification is a problem. Steady readings inside and outside the farm show whether that local lift holds.</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>pH sensors on buoys inside the farm and at a spot outside it</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>pH readings</t>
+        </is>
+      </c>
+      <c r="I14" s="31" t="inlineStr">
+        <is>
+          <t>pH; Carbonate system (pH / OA)</t>
+        </is>
+      </c>
+      <c r="J14" s="31" t="n"/>
+      <c r="K14" s="31" t="n"/>
+      <c r="L14" s="31" t="n"/>
+      <c r="M14" s="31" t="n"/>
+      <c r="N14" s="31" t="n"/>
+      <c r="O14" s="31" t="n"/>
+      <c r="P14" s="31" t="n"/>
+      <c r="Q14" s="31" t="inlineStr">
+        <is>
+          <t>Temperature / salinity; Continuous moored sensors</t>
+        </is>
+      </c>
+      <c r="R14" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take pH readings?</t>
+        </is>
+      </c>
+      <c r="S14" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T14" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V14" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W14" s="31" t="inlineStr">
+        <is>
+          <t>Monthly or less=0.4; Weekly=1; Daily, or with a logger=1</t>
+        </is>
+      </c>
+      <c r="X14" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least weekly, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z14" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA14" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD14" s="31" t="inlineStr">
+        <is>
+          <t>A pH sensor on a buoy inside the farm and another at a spot outside it, logging at least weekly.</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>A pH sensor on a buoy inside the farm and another at a spot outside it, logging at least weekly.</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-1.1.1</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Life growing on your gear and shellfish</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>The small plants and animals that live on your lines, gear and shellfish, such as sponges, tube worms, small crabs and seaweeds. Plenty of native species, and many different kinds, suggest your farm is giving local life a place to live.</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>Close-up of native plants and animals living on a line</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>Checks of gear or stock</t>
+        </is>
+      </c>
+      <c r="I15" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota on lines / structures; Epifauna on crop / rope; Invertebrate collectors / fauna traps; Settlement plates / artificial substrata</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="n"/>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="31" t="n"/>
+      <c r="M15" s="31" t="n"/>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="31" t="n"/>
+      <c r="R15" s="31" t="inlineStr">
+        <is>
+          <t>Where do you check?</t>
+        </is>
+      </c>
+      <c r="S15" s="31" t="inlineStr">
+        <is>
+          <t>Inside the farm only=0.5; Inside and at the edge of the farm=1</t>
+        </is>
+      </c>
+      <c r="T15" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" s="31" t="inlineStr">
+        <is>
+          <t>Add checks at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V15" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W15" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X15" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y15" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="Z15" s="31" t="inlineStr">
+        <is>
+          <t>What do you note down?</t>
+        </is>
+      </c>
+      <c r="AA15" s="31" t="inlineStr">
+        <is>
+          <t>Counts and names (species or groups)=1; What’s there, without counts=0.5; Only whether there’s fouling=0</t>
+        </is>
+      </c>
+      <c r="AB15" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="31" t="inlineStr">
+        <is>
+          <t>Count what you find and name it to species or group; that gives the abundance and diversity the Framework asks for.</t>
+        </is>
+      </c>
+      <c r="AD15" s="31" t="inlineStr">
+        <is>
+          <t>Pull a section of line or a few animals each season and count what’s living on them.</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Pull a section of line each season and count what’s living on it.</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Mobile fauna</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-1.2.1</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Fish, crabs and other visitors</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Fish, crabs, birds and other animals that move around and use your farm. Counting what visits, and how many kinds, shows whether the farm works as habitat, without adding extra fishing pressure.</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line records the fish and other animals that visit</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>Video or visual counts</t>
+        </is>
+      </c>
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects; Nets &amp; baited traps; Towed video / ROV</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="n"/>
+      <c r="K16" s="31" t="n"/>
+      <c r="L16" s="31" t="n"/>
+      <c r="M16" s="31" t="n"/>
+      <c r="N16" s="31" t="n"/>
+      <c r="O16" s="31" t="n"/>
+      <c r="P16" s="31" t="n"/>
+      <c r="Q16" s="31" t="n"/>
+      <c r="R16" s="31" t="inlineStr">
+        <is>
+          <t>Where do you check?</t>
+        </is>
+      </c>
+      <c r="S16" s="31" t="inlineStr">
+        <is>
+          <t>Inside the farm only=0.5; Inside and at the edge of the farm=1</t>
+        </is>
+      </c>
+      <c r="T16" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" s="31" t="inlineStr">
+        <is>
+          <t>Add checks at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V16" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W16" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X16" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y16" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="Z16" s="31" t="inlineStr">
+        <is>
+          <t>What do you note down?</t>
+        </is>
+      </c>
+      <c r="AA16" s="31" t="inlineStr">
+        <is>
+          <t>Counts and names (species or groups)=1; What’s there, without counts=0.5; Not much detail=0</t>
+        </is>
+      </c>
+      <c r="AB16" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="31" t="inlineStr">
+        <is>
+          <t>Count what you find and name it to species or group.</t>
+        </is>
+      </c>
+      <c r="AD16" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line (a GoPro works), set once a season inside the farm and at its edge. Most AquaPIP protocols for this are Practitioner (T1), so you can run them yourself.</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>A camera on a line (a GoPro works), once a season, inside the farm and at its edge.</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.3.1</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-1.3.1</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>Animals living in the seabed under your farm</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Worms, clams and other small animals that live buried in the seabed under and around your farm. A healthy mix of them shows the seabed is coping well with the farm above. They’re collected with a grab or core and sorted later.</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>A grab sample from the seabed under the farm</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>Seabed animal samples</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna community</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="31" t="n"/>
+      <c r="M17" s="31" t="n"/>
+      <c r="N17" s="31" t="n"/>
+      <c r="O17" s="31" t="n"/>
+      <c r="P17" s="31" t="n"/>
+      <c r="Q17" s="31" t="n"/>
+      <c r="R17" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take seabed samples?</t>
+        </is>
+      </c>
+      <c r="S17" s="31" t="inlineStr">
+        <is>
+          <t>Under the farm only=0.5; Under the farm and at its edge=1</t>
+        </is>
+      </c>
+      <c r="T17" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="31" t="inlineStr">
+        <is>
+          <t>Add seabed samples at the edge of the farm.</t>
+        </is>
+      </c>
+      <c r="V17" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W17" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X17" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y17" s="31" t="inlineStr">
+        <is>
+          <t>Sample once a season.</t>
+        </is>
+      </c>
+      <c r="Z17" s="31" t="inlineStr">
+        <is>
+          <t>Who sorts and identifies the animals?</t>
+        </is>
+      </c>
+      <c r="AA17" s="31" t="inlineStr">
+        <is>
+          <t>A lab or trained partner=1; We sort them ourselves=0.6</t>
+        </is>
+      </c>
+      <c r="AB17" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC17" s="31" t="inlineStr">
+        <is>
+          <t>Send samples to a lab or trained partner to sort and identify.</t>
+        </is>
+      </c>
+      <c r="AD17" s="31" t="inlineStr">
+        <is>
+          <t>Seabed grabs or cores under the farm and at its edge each season, with a lab to sort them.</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Seabed grabs or cores under the farm and at its edge each season, with a lab to sort them.</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.4.1</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Sediment characteristics</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-1.4.1</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>The health of the seabed under your farm</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>What the seabed under your farm is like: how much organic matter it holds, and whether it has enough oxygen or smells of rotten eggs (sulfide). Shellfish drop waste onto the seabed, so comparing it with nearby seabed shows whether it stays as healthy as the surroundings.</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>Seabed cores under the farm and at a similar spot nearby</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>Seabed condition</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>Sediment chemistry (OC / TN / redox / AVS); Sediment-profile imaging (SPI); MOM-B condition survey; Grain size / particle size</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="n"/>
+      <c r="K18" s="31" t="n"/>
+      <c r="L18" s="31" t="n"/>
+      <c r="M18" s="31" t="n"/>
+      <c r="N18" s="31" t="n"/>
+      <c r="O18" s="31" t="n"/>
+      <c r="P18" s="31" t="n"/>
+      <c r="Q18" s="31" t="inlineStr">
+        <is>
+          <t>Biodeposition traps</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="inlineStr">
+        <is>
+          <t>Where do you sample the seabed?</t>
+        </is>
+      </c>
+      <c r="S18" s="31" t="inlineStr">
+        <is>
+          <t>Under the farm only=0.5; Under the farm and at a similar spot nearby=1</t>
+        </is>
+      </c>
+      <c r="T18" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" s="31" t="inlineStr">
+        <is>
+          <t>Add a seabed sample at a similar spot nearby, away from the farm.</t>
+        </is>
+      </c>
+      <c r="V18" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W18" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Twice a year or every season=1</t>
+        </is>
+      </c>
+      <c r="X18" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y18" s="31" t="inlineStr">
+        <is>
+          <t>Sample at least twice a year.</t>
+        </is>
+      </c>
+      <c r="Z18" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA18" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB18" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD18" s="31" t="inlineStr">
+        <is>
+          <t>Seabed cores under the farm and at a similar spot nearby, twice a year, checked for organic matter and sulfide.</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Seabed cores under the farm and at a similar spot nearby, twice a year, checked for organic matter and sulfide.</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.1.1</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Associated community composition</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-2.1.1</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>All the life at your farm, compared with nearby</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>The whole community of life at your farm: on the gear, swimming around it and living in the seabed below. Comparing it with similar habitat nearby shows whether your farm adds to local biodiversity, not just matches it.</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>Life on the gear, in the water and in the seabed, compared with similar habitat nearby</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>Life on the gear (epibiota)</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="inlineStr">
+        <is>
+          <t>Epibiota on lines / structures; Epifauna on crop / rope; Invertebrate collectors / fauna traps; Settlement plates / artificial substrata</t>
+        </is>
+      </c>
+      <c r="J19" s="31" t="n"/>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>Fish and other mobile animals</t>
+        </is>
+      </c>
+      <c r="L19" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects; Nets &amp; baited traps; Towed video / ROV</t>
+        </is>
+      </c>
+      <c r="M19" s="31" t="inlineStr">
+        <is>
+          <t>a camera on a line works</t>
+        </is>
+      </c>
+      <c r="N19" s="31" t="inlineStr">
+        <is>
+          <t>Seabed animals (infauna)</t>
+        </is>
+      </c>
+      <c r="O19" s="31" t="inlineStr">
+        <is>
+          <t>Benthic infauna community</t>
+        </is>
+      </c>
+      <c r="P19" s="31" t="inlineStr">
+        <is>
+          <t>sediment grabs or cores</t>
+        </is>
+      </c>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="31" t="inlineStr">
+        <is>
+          <t>Do you also survey similar habitat outside the farm?</t>
+        </is>
+      </c>
+      <c r="S19" s="31" t="inlineStr">
+        <is>
+          <t>No, inside only=0.5; Yes=1</t>
+        </is>
+      </c>
+      <c r="T19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="31" t="inlineStr">
+        <is>
+          <t>Add a similar habitat outside the farm to compare against.</t>
+        </is>
+      </c>
+      <c r="V19" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W19" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X19" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="31" t="inlineStr">
+        <is>
+          <t>Survey once a season.</t>
+        </is>
+      </c>
+      <c r="Z19" s="31" t="n"/>
+      <c r="AA19" s="31" t="n"/>
+      <c r="AB19" s="31" t="n"/>
+      <c r="AC19" s="31" t="n"/>
+      <c r="AD19" s="31" t="inlineStr">
+        <is>
+          <t>Start with one part, such as counts of life on your gear, and add the others over time.</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Start with one part, such as counts of life on your gear, and add the others over time.</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.2.1</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Spawning / recruitment</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-2.2.1</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>Young fish and animals settling at your farm</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Signs that fish, invertebrates or seaweeds breed at your farm, or that their young settle and grow there. Simple traps that young fish shelter in, or baskets hung on the lines, collect them. It shows whether your farm works as a nursery.</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>Settlement traps hung in the farm collect young fish and animals</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>Settlement traps or baskets</t>
+        </is>
+      </c>
+      <c r="I20" s="31" t="inlineStr">
+        <is>
+          <t>Settlement plates / artificial substrata; Invertebrate collectors / fauna traps</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="31" t="n"/>
+      <c r="N20" s="31" t="n"/>
+      <c r="O20" s="31" t="n"/>
+      <c r="P20" s="31" t="n"/>
+      <c r="Q20" s="31" t="n"/>
+      <c r="R20" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="S20" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="T20" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U20" s="31" t="inlineStr">
+        <is>
+          <t>Check once a season.</t>
+        </is>
+      </c>
+      <c r="V20" s="31" t="inlineStr">
+        <is>
+          <t>What do you note down?</t>
+        </is>
+      </c>
+      <c r="W20" s="31" t="inlineStr">
+        <is>
+          <t>Counts and names (species or groups)=1; What’s there, without counts=0.5; Not much detail=0</t>
+        </is>
+      </c>
+      <c r="X20" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="31" t="inlineStr">
+        <is>
+          <t>Count what you find and name it to species or group.</t>
+        </is>
+      </c>
+      <c r="Z20" s="31" t="n"/>
+      <c r="AA20" s="31" t="n"/>
+      <c r="AB20" s="31" t="n"/>
+      <c r="AC20" s="31" t="n"/>
+      <c r="AD20" s="31" t="inlineStr">
+        <is>
+          <t>Hang a few settlement traps or baskets in the farm each season and count what settles in them.</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Hang a few settlement traps or baskets in the farm each season and count what settles in them.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 3.1.1</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Larval supply to wild populations</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_HB-3.1.1</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Your shellfish’s young helping wild beds</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Where wild shellfish of the same species have declined, larvae spawned on your farm can drift out and settle on wild beds. Tracing farm-born young in the wild, using chemical fingerprints in their shells, shows whether your farm helps those beds recover while keeping their genetics healthy.</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>Larvae drift from the farm and settle on a wild shellfish bed</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="inlineStr">
+        <is>
+          <t>Tracing or modelling larvae</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="inlineStr">
+        <is>
+          <t>Hydrodynamic + particle tracking</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>shell fingerprinting needs a research partner</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="n"/>
+      <c r="L21" s="31" t="n"/>
+      <c r="M21" s="31" t="n"/>
+      <c r="N21" s="31" t="n"/>
+      <c r="O21" s="31" t="n"/>
+      <c r="P21" s="31" t="n"/>
+      <c r="Q21" s="31" t="n"/>
+      <c r="R21" s="31" t="inlineStr">
+        <is>
+          <t>Do you also sample nearby wild beds?</t>
+        </is>
+      </c>
+      <c r="S21" s="31" t="inlineStr">
+        <is>
+          <t>No=0.5; Yes=1</t>
+        </is>
+      </c>
+      <c r="T21" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" s="31" t="inlineStr">
+        <is>
+          <t>Add sampling on nearby wild beds.</t>
+        </is>
+      </c>
+      <c r="V21" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W21" s="31" t="inlineStr">
+        <is>
+          <t>Once a year or less=0.4; Every season=1</t>
+        </is>
+      </c>
+      <c r="X21" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="31" t="inlineStr">
+        <is>
+          <t>Sample once a season.</t>
+        </is>
+      </c>
+      <c r="Z21" s="31" t="n"/>
+      <c r="AA21" s="31" t="n"/>
+      <c r="AB21" s="31" t="n"/>
+      <c r="AC21" s="31" t="n"/>
+      <c r="AD21" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: modelling where larvae drift, or tracing farm-born young on nearby wild beds.</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: modelling where larvae drift, or tracing farm-born young on nearby wild beds.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.1.1</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>N &amp; P bioextraction</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-1.1.1</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Nutrients your harvest takes out of the water</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>The nitrogen and phosphorus your shellfish build into their bodies. At harvest those nutrients leave the water with the crop, so less is left to feed algal blooms. It’s worked out from your harvest weights and published values for your species.</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>Nutrients built into your shellfish leave the water at harvest</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="n"/>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="31" t="n"/>
+      <c r="M22" s="31" t="n"/>
+      <c r="N22" s="31" t="n"/>
+      <c r="O22" s="31" t="n"/>
+      <c r="P22" s="31" t="n"/>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>Bivalve condition index / growth; Tissue elemental (CHN) analysis</t>
+        </is>
+      </c>
+      <c r="R22" s="31" t="inlineStr">
+        <is>
+          <t>Do you weigh every harvest?</t>
+        </is>
+      </c>
+      <c r="S22" s="31" t="inlineStr">
+        <is>
+          <t>Every harvest=1; Some harvests=0.5</t>
+        </is>
+      </c>
+      <c r="T22" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" s="31" t="inlineStr">
+        <is>
+          <t>Weigh every harvest, or count it and convert to weight.</t>
+        </is>
+      </c>
+      <c r="V22" s="31" t="inlineStr">
+        <is>
+          <t>Where do your harvest weights end up?</t>
+        </is>
+      </c>
+      <c r="W22" s="31" t="inlineStr">
+        <is>
+          <t>One logbook or spreadsheet=1; Spread across receipts or memory=0.3</t>
+        </is>
+      </c>
+      <c r="X22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="31" t="inlineStr">
+        <is>
+          <t>Keep the year’s harvest weights together in one log.</t>
+        </is>
+      </c>
+      <c r="Z22" s="31" t="n"/>
+      <c r="AA22" s="31" t="n"/>
+      <c r="AB22" s="31" t="n"/>
+      <c r="AC22" s="31" t="n"/>
+      <c r="AD22" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest. That, plus published N and P values for your species, is all this indicator needs.</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest; with published N and P values for your species, that’s all this needs.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.1.2</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Denitrification rate</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-1.1.2</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>Nitrogen turned back into harmless gas</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Bacteria in the seabed under shellfish farms can turn nitrogen from the water into harmless nitrogen gas, removing it for good. A sealed chamber on the seabed measures how fast that happens under the farm and at a nearby spot without shellfish.</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>Sealed chambers on the seabed, under the farm and at a nearby spot, measure nitrogen gas</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>Seabed chamber measurements</t>
+        </is>
+      </c>
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>Sediment / benthic flux incubation</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="n"/>
+      <c r="K23" s="31" t="n"/>
+      <c r="L23" s="31" t="n"/>
+      <c r="M23" s="31" t="n"/>
+      <c r="N23" s="31" t="n"/>
+      <c r="O23" s="31" t="n"/>
+      <c r="P23" s="31" t="n"/>
+      <c r="Q23" s="31" t="n"/>
+      <c r="R23" s="31" t="inlineStr">
+        <is>
+          <t>Where do you measure?</t>
+        </is>
+      </c>
+      <c r="S23" s="31" t="inlineStr">
+        <is>
+          <t>Under the farm only=0.5; Under the farm and at a nearby spot without shellfish=1</t>
+        </is>
+      </c>
+      <c r="T23" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" s="31" t="inlineStr">
+        <is>
+          <t>Add a chamber at a nearby spot without shellfish.</t>
+        </is>
+      </c>
+      <c r="V23" s="31" t="inlineStr">
+        <is>
+          <t>When did you last measure?</t>
+        </is>
+      </c>
+      <c r="W23" s="31" t="inlineStr">
+        <is>
+          <t>Within the last year=1; Longer ago=0.4</t>
+        </is>
+      </c>
+      <c r="X23" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="31" t="inlineStr">
+        <is>
+          <t>Repeat the measurement with your current stock.</t>
+        </is>
+      </c>
+      <c r="Z23" s="31" t="n"/>
+      <c r="AA23" s="31" t="n"/>
+      <c r="AB23" s="31" t="n"/>
+      <c r="AC23" s="31" t="n"/>
+      <c r="AD23" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: sealed chambers on the seabed under the farm and at a nearby spot without shellfish.</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: sealed chambers on the seabed under the farm and at a nearby spot without shellfish.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.2.1</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-1.2.1</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen in the water around your farm</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>How much oxygen is dissolved in the water. Too many nutrients can push oxygen down, which stresses fish and shellfish. Comparing readings inside and outside the farm shows whether your farm is helping ease that pressure.</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen readings inside the farm and at a spot outside it</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>Oxygen readings</t>
+        </is>
+      </c>
+      <c r="I24" s="31" t="inlineStr">
+        <is>
+          <t>Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="31" t="n"/>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="31" t="n"/>
+      <c r="P24" s="31" t="n"/>
+      <c r="Q24" s="31" t="inlineStr">
+        <is>
+          <t>Temperature / salinity; Continuous moored sensors</t>
+        </is>
+      </c>
+      <c r="R24" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take oxygen readings?</t>
+        </is>
+      </c>
+      <c r="S24" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T24" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V24" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W24" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X24" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z24" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA24" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD24" s="31" t="inlineStr">
+        <is>
+          <t>A handheld oxygen meter, read at the same time of day inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>A handheld oxygen meter, read at the same time of day inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>WQ 1.3.1</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Water filtration rate</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-1.3.1</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>How much water your shellfish clean</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>The volume of water your shellfish filter as they feed. Filtering takes out particles and algae, letting more light reach the seabed and helping prevent low-oxygen water. It’s worked out from how many animals you have and how big they are.</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>Shellfish filter particles out of the water flowing through the farm</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr">
+        <is>
+          <t>Stock numbers by size class</t>
+        </is>
+      </c>
+      <c r="I25" s="31" t="inlineStr">
+        <is>
+          <t>Stock numbers by size class</t>
+        </is>
+      </c>
+      <c r="J25" s="31" t="n"/>
+      <c r="K25" s="31" t="inlineStr">
+        <is>
+          <t>Animal size or meat weight</t>
+        </is>
+      </c>
+      <c r="L25" s="31" t="inlineStr">
+        <is>
+          <t>Bivalve condition index / growth</t>
+        </is>
+      </c>
+      <c r="M25" s="31" t="n"/>
+      <c r="N25" s="31" t="n"/>
+      <c r="O25" s="31" t="n"/>
+      <c r="P25" s="31" t="n"/>
+      <c r="Q25" s="31" t="n"/>
+      <c r="R25" s="31" t="inlineStr">
+        <is>
+          <t>When did you last count stock by size class?</t>
+        </is>
+      </c>
+      <c r="S25" s="31" t="inlineStr">
+        <is>
+          <t>Within the last year=1; More than a year ago=0.4</t>
+        </is>
+      </c>
+      <c r="T25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="31" t="inlineStr">
+        <is>
+          <t>Update your stock count by size class; once a year is enough.</t>
+        </is>
+      </c>
+      <c r="V25" s="31" t="inlineStr">
+        <is>
+          <t>Do you measure shell length or meat weight for each size class?</t>
+        </is>
+      </c>
+      <c r="W25" s="31" t="inlineStr">
+        <is>
+          <t>Yes, every class=1; Some classes=0.5; Not by class=0</t>
+        </is>
+      </c>
+      <c r="X25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="31" t="inlineStr">
+        <is>
+          <t>Measure a sample from each size class (shell length or dried meat weight).</t>
+        </is>
+      </c>
+      <c r="Z25" s="31" t="n"/>
+      <c r="AA25" s="31" t="n"/>
+      <c r="AB25" s="31" t="n"/>
+      <c r="AC25" s="31" t="n"/>
+      <c r="AD25" s="31" t="inlineStr">
+        <is>
+          <t>Count your stock by size class once a year and measure a sample from each class.</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Count your stock by size class once a year and measure a sample from each class.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Next stop: the Filtration Service Estimator turns your stock and size numbers into a farm filtration rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>WQ 2.1.1</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-2.1.1</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>Tiny algae floating in the water</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>How much microscopic algae (phytoplankton) is floating in the water. Lots of it is a common sign of too many nutrients. Comparing inside and outside the farm shows whether your farm helps keep algae in check, without taking so much that wild shellfish or other farms go short.</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>Water samples inside and outside the farm show how much algae is in it</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll readings</t>
+        </is>
+      </c>
+      <c r="I26" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a (water)</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="31" t="n"/>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="31" t="n"/>
+      <c r="N26" s="31" t="n"/>
+      <c r="O26" s="31" t="n"/>
+      <c r="P26" s="31" t="n"/>
+      <c r="Q26" s="31" t="inlineStr">
+        <is>
+          <t>Water clarity / turbidity (Secchi); Temperature / salinity; Satellite ocean colour (chl-a)</t>
+        </is>
+      </c>
+      <c r="R26" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take water samples?</t>
+        </is>
+      </c>
+      <c r="S26" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T26" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V26" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W26" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X26" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z26" s="31" t="inlineStr">
+        <is>
+          <t>Do you write each reading down?</t>
+        </is>
+      </c>
+      <c r="AA26" s="31" t="inlineStr">
+        <is>
+          <t>Every time=1; Sometimes=0.5; Not usually=0</t>
+        </is>
+      </c>
+      <c r="AB26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="31" t="inlineStr">
+        <is>
+          <t>Write down the date, time, place and reading on every visit.</t>
+        </is>
+      </c>
+      <c r="AD26" s="31" t="inlineStr">
+        <is>
+          <t>Water samples sent to a lab, or a chlorophyll sensor, inside the farm and at a spot outside it. AquaPIP’s protocols for this are Partnership (T2): fieldwork by you, lab work by a partner.</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Lab water samples, or a chlorophyll sensor, inside the farm and at a spot outside it.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>WQ 2.1.2</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Microorganism &amp; plankton community</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_WQ-2.1.2</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>The tiny life drifting in the water</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>Which microscopic plants, animals and microbes drift in the water, and how many. Shellfish feed on some of them, so sampling inside and outside the farm shows whether these communities stay healthy around your farm. Samples go to a lab for microscopy or DNA.</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>A plankton net and water samples inside and outside the farm</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr">
+        <is>
+          <t>Plankton samples</t>
+        </is>
+      </c>
+      <c r="I27" s="31" t="inlineStr">
+        <is>
+          <t>Phytoplankton community (microscopy); Zooplankton net haul; Flow cytometry; Water eDNA; Size-fractionated pigments (HPLC)</t>
+        </is>
+      </c>
+      <c r="J27" s="31" t="n"/>
+      <c r="K27" s="31" t="n"/>
+      <c r="L27" s="31" t="n"/>
+      <c r="M27" s="31" t="n"/>
+      <c r="N27" s="31" t="n"/>
+      <c r="O27" s="31" t="n"/>
+      <c r="P27" s="31" t="n"/>
+      <c r="Q27" s="31" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a (water)</t>
+        </is>
+      </c>
+      <c r="R27" s="31" t="inlineStr">
+        <is>
+          <t>Where do you take plankton samples?</t>
+        </is>
+      </c>
+      <c r="S27" s="31" t="inlineStr">
+        <is>
+          <t>Only inside the farm=0.5; Inside the farm and at a spot outside it=1</t>
+        </is>
+      </c>
+      <c r="T27" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" s="31" t="inlineStr">
+        <is>
+          <t>Add a comparison spot outside the farm, in similar water.</t>
+        </is>
+      </c>
+      <c r="V27" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W27" s="31" t="inlineStr">
+        <is>
+          <t>Once or twice a year=0.4; Every season=1; Monthly or more often=1</t>
+        </is>
+      </c>
+      <c r="X27" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="31" t="inlineStr">
+        <is>
+          <t>Take readings at least once a season, at the same time of day.</t>
+        </is>
+      </c>
+      <c r="Z27" s="31" t="inlineStr">
+        <is>
+          <t>Who identifies what’s in the samples?</t>
+        </is>
+      </c>
+      <c r="AA27" s="31" t="inlineStr">
+        <is>
+          <t>A lab or trained partner=1; We look ourselves=0.5</t>
+        </is>
+      </c>
+      <c r="AB27" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="31" t="inlineStr">
+        <is>
+          <t>Send samples to a lab or trained partner for identification.</t>
+        </is>
+      </c>
+      <c r="AD27" s="31" t="inlineStr">
+        <is>
+          <t>Plankton net tows and water samples inside and outside the farm each season, identified by a lab.</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Plankton net tows and water samples inside and outside the farm each season, identified by a lab.</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>CC 1.1.1</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Cradle-to-grave GHG emissions</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_CC-1.1.1</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>Your product’s carbon footprint, start to finish</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>All the greenhouse gas released to produce your shellfish, from seed and gear through boat fuel and processing to getting it to market. Comparing it with similar foods shows whether yours is a low-carbon choice, and tracking it each year shows whether it’s coming down.</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>Emissions counted from seed and gear to boat, truck and market</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr">
+        <is>
+          <t>Fuel and energy records</t>
+        </is>
+      </c>
+      <c r="I28" s="31" t="inlineStr">
+        <is>
+          <t>Fuel and energy use</t>
+        </is>
+      </c>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="31" t="n"/>
+      <c r="M28" s="31" t="n"/>
+      <c r="N28" s="31" t="n"/>
+      <c r="O28" s="31" t="n"/>
+      <c r="P28" s="31" t="n"/>
+      <c r="Q28" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="R28" s="31" t="inlineStr">
+        <is>
+          <t>What does your tally cover?</t>
+        </is>
+      </c>
+      <c r="S28" s="31" t="inlineStr">
+        <is>
+          <t>Inputs (seed, gear), farm fuel and transport to market=1; Farm fuel and energy only=0.5</t>
+        </is>
+      </c>
+      <c r="T28" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" s="31" t="inlineStr">
+        <is>
+          <t>Add inputs (seed, gear) and transport to market to your tally.</t>
+        </is>
+      </c>
+      <c r="V28" s="31" t="inlineStr">
+        <is>
+          <t>How often do you add it up?</t>
+        </is>
+      </c>
+      <c r="W28" s="31" t="inlineStr">
+        <is>
+          <t>Every year=1; Less often=0.4</t>
+        </is>
+      </c>
+      <c r="X28" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="31" t="inlineStr">
+        <is>
+          <t>Add it up every year so you can see the trend.</t>
+        </is>
+      </c>
+      <c r="Z28" s="31" t="n"/>
+      <c r="AA28" s="31" t="n"/>
+      <c r="AB28" s="31" t="n"/>
+      <c r="AC28" s="31" t="n"/>
+      <c r="AD28" s="31" t="inlineStr">
+        <is>
+          <t>Keep a yearly tally of fuel, electricity and your main inputs (seed, gear, transport). A footprint calculator or partner can turn it into emissions.</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>A yearly tally of fuel, electricity and main inputs, turned into emissions with a footprint calculator.</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>CC 2.1.1</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Shell / pearl carbon retention</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_CC-2.1.1</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Carbon held in your shells, and where they go</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>Shellfish build their shells partly from carbon. This tracks how much carbon your harvested shells hold, and whether the shells end up somewhere that keeps it locked away, such as shell recycling for reef restoration. It’s worked out from harvest weight and published values.</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="inlineStr">
+        <is>
+          <t>Carbon in harvested shells, and where the shells end up</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights</t>
+        </is>
+      </c>
+      <c r="I29" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="J29" s="31" t="n"/>
+      <c r="K29" s="31" t="inlineStr">
+        <is>
+          <t>Where the shells go</t>
+        </is>
+      </c>
+      <c r="L29" s="31" t="inlineStr">
+        <is>
+          <t>Harvest and shell end uses</t>
+        </is>
+      </c>
+      <c r="M29" s="31" t="inlineStr">
+        <is>
+          <t>buyer, processor or recycling records</t>
+        </is>
+      </c>
+      <c r="N29" s="31" t="n"/>
+      <c r="O29" s="31" t="n"/>
+      <c r="P29" s="31" t="n"/>
+      <c r="Q29" s="31" t="n"/>
+      <c r="R29" s="31" t="inlineStr">
+        <is>
+          <t>Do you weigh every harvest?</t>
+        </is>
+      </c>
+      <c r="S29" s="31" t="inlineStr">
+        <is>
+          <t>Every harvest=1; Some harvests=0.5</t>
+        </is>
+      </c>
+      <c r="T29" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="31" t="inlineStr">
+        <is>
+          <t>Weigh every harvest, or count it and convert to weight.</t>
+        </is>
+      </c>
+      <c r="V29" s="31" t="inlineStr">
+        <is>
+          <t>Where do your harvest weights end up?</t>
+        </is>
+      </c>
+      <c r="W29" s="31" t="inlineStr">
+        <is>
+          <t>One logbook or spreadsheet=1; Spread across receipts or memory=0.3</t>
+        </is>
+      </c>
+      <c r="X29" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="31" t="inlineStr">
+        <is>
+          <t>Keep the year’s harvest weights together in one log.</t>
+        </is>
+      </c>
+      <c r="Z29" s="31" t="n"/>
+      <c r="AA29" s="31" t="n"/>
+      <c r="AB29" s="31" t="n"/>
+      <c r="AC29" s="31" t="n"/>
+      <c r="AD29" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest and keep a note of where the shells end up.</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Weigh each harvest and keep a note of where the shells end up.</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>Molluscs &amp; Echinoderms</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>CC 3.1.1</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Wave attenuation / coastal protection</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>mollusc_CC-3.1.1</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>How much your farm calms the waves</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>How much smaller waves are after they pass through your farm. Lines and shellfish can take energy out of waves, which may help protect the shore from erosion in storms. Wave buoys on either side of the farm measure the difference.</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>Wave buoys on either side of the farm show how much the waves shrink</t>
+        </is>
+      </c>
+      <c r="H30" s="31" t="inlineStr">
+        <is>
+          <t>Wave measurements</t>
+        </is>
+      </c>
+      <c r="I30" s="31" t="inlineStr">
+        <is>
+          <t>Wave-tide recorder; ADCP (currents / waves)</t>
+        </is>
+      </c>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="31" t="n"/>
+      <c r="P30" s="31" t="n"/>
+      <c r="Q30" s="31" t="inlineStr">
+        <is>
+          <t>Wave-attenuation model; Site exposure characterisation</t>
+        </is>
+      </c>
+      <c r="R30" s="31" t="inlineStr">
+        <is>
+          <t>Where are your wave loggers?</t>
+        </is>
+      </c>
+      <c r="S30" s="31" t="inlineStr">
+        <is>
+          <t>One side of the farm only=0.5; On both sides of the farm=1</t>
+        </is>
+      </c>
+      <c r="T30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="31" t="inlineStr">
+        <is>
+          <t>Put a wave logger on each side of the farm.</t>
+        </is>
+      </c>
+      <c r="V30" s="31" t="inlineStr">
+        <is>
+          <t>How do you record waves?</t>
+        </is>
+      </c>
+      <c r="W30" s="31" t="inlineStr">
+        <is>
+          <t>Spot checks=0.4; A logger running through storms=1</t>
+        </is>
+      </c>
+      <c r="X30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y30" s="31" t="inlineStr">
+        <is>
+          <t>Leave a logger running through the storm season.</t>
+        </is>
+      </c>
+      <c r="Z30" s="31" t="n"/>
+      <c r="AA30" s="31" t="n"/>
+      <c r="AB30" s="31" t="n"/>
+      <c r="AC30" s="31" t="n"/>
+      <c r="AD30" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: wave loggers on the seaward and landward sides of the farm through a storm season.</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Usually a research partnership: wave loggers on the seaward and landward sides of the farm through a storm season.</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>Marine Finfish</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Fauna use of permitted area</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>finfish_HB-1.1.1</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>Wildlife using the area around your pens</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>Marine mammals, large fish and other wildlife that use your permitted area, and whether they do so undisturbed. Logging what you see on every visit, plus a few planned surveys each year, shows whether the area works as a refuge.</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>Dolphins, seabirds and large fish sighted across the permitted area</t>
+        </is>
+      </c>
+      <c r="H31" s="31" t="inlineStr">
+        <is>
+          <t>Wildlife sightings or surveys</t>
+        </is>
+      </c>
+      <c r="I31" s="31" t="inlineStr">
+        <is>
+          <t>Bird / shorebird counts; Visual census / belt transects; Passive acoustic (marine mammals); Towed video / ROV; Time-lapse / GoPro cameras</t>
+        </is>
+      </c>
+      <c r="J31" s="31" t="n"/>
+      <c r="K31" s="31" t="n"/>
+      <c r="L31" s="31" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="31" t="n"/>
+      <c r="Q31" s="31" t="n"/>
+      <c r="R31" s="31" t="inlineStr">
+        <is>
+          <t>How do you record wildlife?</t>
+        </is>
+      </c>
+      <c r="S31" s="31" t="inlineStr">
+        <is>
+          <t>Sightings on every visit plus planned surveys=1; Sightings only=0.5; Now and then=0.3</t>
+        </is>
+      </c>
+      <c r="T31" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" s="31" t="inlineStr">
+        <is>
+          <t>Log sightings on every visit and add a planned survey each season.</t>
+        </is>
+      </c>
+      <c r="V31" s="31" t="inlineStr">
+        <is>
+          <t>Where do you look?</t>
+        </is>
+      </c>
+      <c r="W31" s="31" t="inlineStr">
+        <is>
+          <t>Near the pens only=0.5; Across the whole permitted area=1</t>
+        </is>
+      </c>
+      <c r="X31" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="31" t="inlineStr">
+        <is>
+          <t>Survey across the whole permitted area, not just near the pens.</t>
+        </is>
+      </c>
+      <c r="Z31" s="31" t="n"/>
+      <c r="AA31" s="31" t="n"/>
+      <c r="AB31" s="31" t="n"/>
+      <c r="AC31" s="31" t="n"/>
+      <c r="AD31" s="31" t="inlineStr">
+        <is>
+          <t>Log wildlife sightings on every visit, and add one planned survey of the permitted area each season.</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Log wildlife sightings on every visit, and add one planned survey of the permitted area each season.</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Marine Finfish</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Contribution to wild stocks</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>finfish_HB-1.2.1</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish around your pens adding to local stocks</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish that gather around net pens may grow and breed there. This asks whether that adds to regional wild fish stocks, which takes a fisheries stock assessment, often done with fisheries managers. Video of wild fish in the area is a simpler stand-in.</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish around the pens and further out, counted toward regional stocks</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish counts</t>
+        </is>
+      </c>
+      <c r="I32" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects</t>
+        </is>
+      </c>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="inlineStr">
+        <is>
+          <t>Fisheries stock assessment</t>
+        </is>
+      </c>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="inlineStr">
+        <is>
+          <t>usually with fisheries managers</t>
+        </is>
+      </c>
+      <c r="N32" s="31" t="n"/>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
+      <c r="Q32" s="31" t="n"/>
+      <c r="R32" s="31" t="inlineStr">
+        <is>
+          <t>Where do you count wild fish?</t>
+        </is>
+      </c>
+      <c r="S32" s="31" t="inlineStr">
+        <is>
+          <t>Inside the permitted area only=0.5; Inside and outside the area=1</t>
+        </is>
+      </c>
+      <c r="T32" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" s="31" t="inlineStr">
+        <is>
+          <t>Add counts outside the permitted area to compare.</t>
+        </is>
+      </c>
+      <c r="V32" s="31" t="inlineStr">
+        <is>
+          <t>How often?</t>
+        </is>
+      </c>
+      <c r="W32" s="31" t="inlineStr">
+        <is>
+          <t>Less than once a year=0.4; Every year=1</t>
+        </is>
+      </c>
+      <c r="X32" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="31" t="inlineStr">
+        <is>
+          <t>Repeat it every year.</t>
+        </is>
+      </c>
+      <c r="Z32" s="31" t="n"/>
+      <c r="AA32" s="31" t="n"/>
+      <c r="AB32" s="31" t="n"/>
+      <c r="AC32" s="31" t="n"/>
+      <c r="AD32" s="31" t="inlineStr">
+        <is>
+          <t>Start with yearly video counts of wild fish around the pens; a stock assessment usually comes later, with fisheries managers.</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Start with yearly video counts of wild fish around the pens; a stock assessment usually comes later, with fisheries managers.</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Marine Finfish</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.1.1</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Fish attracted to net pens</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>finfish_HB-2.1.1</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish drawn to your pens, and their health</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>Which wild fish gather around your net pens, and whether farmed and wild fish stay free of extra parasites and disease. Regular sea-lice counts and health checks on your stock, plus checks on wild fish nearby, show the pens attract fish without becoming a trap.</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish around the pen, with lice checks on farmed and wild fish</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="inlineStr">
+        <is>
+          <t>Wild fish counts around the pens</t>
+        </is>
+      </c>
+      <c r="I33" s="31" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras; Baited remote underwater video (BRUV); Visual census / belt transects</t>
+        </is>
+      </c>
+      <c r="J33" s="31" t="n"/>
+      <c r="K33" s="31" t="inlineStr">
+        <is>
+          <t>Sea-lice and disease checks</t>
+        </is>
+      </c>
+      <c r="L33" s="31" t="inlineStr">
+        <is>
+          <t>Sea-lice and disease checks on stock</t>
+        </is>
+      </c>
+      <c r="M33" s="31" t="n"/>
+      <c r="N33" s="31" t="n"/>
+      <c r="O33" s="31" t="n"/>
+      <c r="P33" s="31" t="n"/>
+      <c r="Q33" s="31" t="n"/>
+      <c r="R33" s="31" t="inlineStr">
+        <is>
+          <t>How often do you check farmed fish?</t>
+        </is>
+      </c>
+      <c r="S33" s="31" t="inlineStr">
+        <is>
+          <t>Monthly or less=0.4; Weekly or more=1</t>
+        </is>
+      </c>
+      <c r="T33" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" s="31" t="inlineStr">
+        <is>
+          <t>Check farmed fish at least weekly.</t>
+        </is>
+      </c>
+      <c r="V33" s="31" t="inlineStr">
+        <is>
+          <t>Do you also check wild fish near the pens?</t>
+        </is>
+      </c>
+      <c r="W33" s="31" t="inlineStr">
+        <is>
+          <t>No=0.5; Yes=1</t>
+        </is>
+      </c>
+      <c r="X33" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" s="31" t="inlineStr">
+        <is>
+          <t>Add health checks on wild fish within 2.5 km of the pens.</t>
+        </is>
+      </c>
+      <c r="Z33" s="31" t="n"/>
+      <c r="AA33" s="31" t="n"/>
+      <c r="AB33" s="31" t="n"/>
+      <c r="AC33" s="31" t="n"/>
+      <c r="AD33" s="31" t="inlineStr">
+        <is>
+          <t>Count wild fish around the pens with a camera, and keep up regular sea-lice and health checks on your stock.</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Count wild fish around the pens with a camera, and keep up regular sea-lice and health checks on your stock.</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>Marine Finfish</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>CC 1.1.1</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Cradle-to-grave GHG emissions</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>finfish_CC-1.1.1</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Your product’s carbon footprint, start to finish</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>All the greenhouse gas released to produce your fish, from feed and young fish through boat fuel and processing to getting it to market. Comparing it with similar products shows whether yours is a lower-carbon choice, and tracking it each year shows whether it’s coming down.</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>Emissions counted from feed and young fish to boat, truck and market</t>
+        </is>
+      </c>
+      <c r="H34" s="31" t="inlineStr">
+        <is>
+          <t>Fuel and energy records</t>
+        </is>
+      </c>
+      <c r="I34" s="31" t="inlineStr">
+        <is>
+          <t>Fuel and energy use</t>
+        </is>
+      </c>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="31" t="n"/>
+      <c r="Q34" s="31" t="inlineStr">
+        <is>
+          <t>Harvest weights or counts</t>
+        </is>
+      </c>
+      <c r="R34" s="31" t="inlineStr">
+        <is>
+          <t>What does your tally cover?</t>
+        </is>
+      </c>
+      <c r="S34" s="31" t="inlineStr">
+        <is>
+          <t>Inputs (feed, young fish), farm fuel and transport to market=1; Farm fuel and energy only=0.5</t>
+        </is>
+      </c>
+      <c r="T34" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" s="31" t="inlineStr">
+        <is>
+          <t>Add inputs (feed, young fish) and transport to market to your tally.</t>
+        </is>
+      </c>
+      <c r="V34" s="31" t="inlineStr">
+        <is>
+          <t>How often do you add it up?</t>
+        </is>
+      </c>
+      <c r="W34" s="31" t="inlineStr">
+        <is>
+          <t>Every year=1; Less often=0.4</t>
+        </is>
+      </c>
+      <c r="X34" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="31" t="inlineStr">
+        <is>
+          <t>Add it up every year so you can see the trend.</t>
+        </is>
+      </c>
+      <c r="Z34" s="31" t="n"/>
+      <c r="AA34" s="31" t="n"/>
+      <c r="AB34" s="31" t="n"/>
+      <c r="AC34" s="31" t="n"/>
+      <c r="AD34" s="31" t="inlineStr">
+        <is>
+          <t>Keep a yearly tally of feed, fuel, electricity and transport. A footprint calculator or partner can turn it into emissions.</t>
+        </is>
+      </c>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>A yearly tally of feed, fuel, electricity and transport, turned into emissions with a footprint calculator.</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -5265,7 +9488,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -5312,6 +9534,93 @@
       <c r="A19" t="inlineStr">
         <is>
           <t>These drive the ranking BOOST only - the screener never filters protocols out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Sheet 'Readiness': the 'How close are you?' page. One row per sector x indicator (same codes as MEL_Indicators).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Part 1-3 label / methods: the measurement itself, split into parts when the Framework asks for several. 'methods' lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  exact Sub_Method names from Monitoring_Approaches (semicolon-separated); ticking any one covers that part. Doing the</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  measurement is worth 60 points; a farm covering 1 of 3 parts gets a third of the score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Context methods: shown as useful context, never scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Q1-Q3: follow-up questions against the Framework minimum. Options are 'Answer=credit' pairs (credit 0-1), separated by</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  semicolons; Weight is relative within the row (the questions share the other 40 points); Gap is the to-do shown when an</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  answer earns less than full credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Picture: file name (no extension) in assets/indicators/. Tagline, summary and caption are the farmer-facing text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Monitoring_Approaches category 'Farm records' (Oct 2026): harvest weights, stock by size class, end uses, fuel and energy,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  and finfish health checks. These feed the calculation-based indicators; they carry no AG tags, so they don't change the</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  protocol boost.</t>
         </is>
       </c>
     </row>
